--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -77,7 +77,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -283,7 +283,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -489,7 +489,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -901,7 +901,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -2367,19 +2367,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -21,13 +21,13 @@
     <sheet name="Read Me" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AO$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BH!$A$1:$AO$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DME!$A$1:$AO$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GAE!$A$1:$AO$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">US!$A$1:$AO$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GAE!$A$1:$AO$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ORTHO!$A$1:$AO$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">US!$A$1:$AO$13</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4043,7 +4043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO32"/>
+  <dimension ref="A1:AO30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4244,7 +4244,7 @@
         <v>46245</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L32" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-4</v>
       </c>
       <c r="M2" s="12">
@@ -4358,7 +4358,7 @@
         <v>46266</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-1</v>
       </c>
       <c r="M3" s="12">
@@ -4472,15 +4472,15 @@
         <v>46268</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>166</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ref="M4:M14" ca="1" si="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
         <v>224</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ref="N4:N12" ca="1" si="2">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
         <v>-21</v>
       </c>
       <c r="O4" s="6">
@@ -4558,19 +4558,19 @@
         <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="C5" s="3">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="D5" s="4">
-        <v>551962197</v>
+        <v>552404210</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F5" s="6">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>75</v>
@@ -4582,25 +4582,25 @@
         <v>75</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="K5" s="3">
-        <v>46260</v>
+        <v>46268</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>170</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>175</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-28</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>-21</v>
       </c>
       <c r="O5" s="6">
-        <v>46452</v>
+        <v>46457</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>59</v>
@@ -4624,37 +4624,37 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="Z5" s="7">
-        <v>1769.18</v>
+        <v>1372.91</v>
       </c>
       <c r="AA5" s="7">
-        <v>1510.96</v>
+        <v>1147.73</v>
       </c>
       <c r="AB5" s="7">
-        <v>205.74</v>
+        <v>184.73</v>
       </c>
       <c r="AC5" s="6">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="AD5" s="7">
-        <v>52.48</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="AE5" s="4">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="4">
-        <v>559120111</v>
+        <v>559120113</v>
       </c>
       <c r="AK5" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>80</v>
@@ -4666,57 +4666,55 @@
         <v>53</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46141</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="4">
-        <v>552404210</v>
+        <v>552644739</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" s="6">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="K6" s="3">
         <v>46268</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>175</v>
-      </c>
-      <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>224</v>
-      </c>
-      <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>176</v>
+      </c>
+      <c r="M6" s="12" t="str">
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N6" s="12" t="str">
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v/>
       </c>
       <c r="O6" s="6">
-        <v>46457</v>
+        <v>46458</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>59</v>
@@ -4743,34 +4741,30 @@
         <v>49</v>
       </c>
       <c r="Z6" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA6" s="7">
-        <v>1147.73</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="7">
-        <v>184.73</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>46141</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="6"/>
       <c r="AD6" s="7">
-        <v>40.450000000000003</v>
+        <v>1426.25</v>
       </c>
       <c r="AE6" s="4">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
-      <c r="AJ6" s="4">
-        <v>559120113</v>
-      </c>
+      <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="AL6" s="5" t="s">
         <v>80</v>
@@ -4782,55 +4776,57 @@
         <v>53</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>456</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46141</v>
+      </c>
       <c r="D7" s="4">
-        <v>552644739</v>
+        <v>552606577</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F7" s="6">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="K7" s="3">
         <v>46268</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>176</v>
-      </c>
-      <c r="M7" s="12" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N7" s="12" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>177</v>
+      </c>
+      <c r="M7" s="12">
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>224</v>
+      </c>
+      <c r="N7" s="12">
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <v>-21</v>
       </c>
       <c r="O7" s="6">
-        <v>46458</v>
+        <v>46459</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>59</v>
@@ -4860,30 +4856,34 @@
         <v>1426.25</v>
       </c>
       <c r="AA7" s="7">
-        <v>0</v>
+        <v>1184.69</v>
       </c>
       <c r="AB7" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="6"/>
+        <v>198.17</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>46141</v>
+      </c>
       <c r="AD7" s="7">
-        <v>1426.25</v>
+        <v>43.39</v>
       </c>
       <c r="AE7" s="4">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="4"/>
+      <c r="AJ7" s="4">
+        <v>559120100</v>
+      </c>
       <c r="AK7" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AM7" s="6">
         <v>46119</v>
@@ -4892,7 +4892,7 @@
         <v>53</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
@@ -4900,46 +4900,46 @@
         <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C8" s="3">
-        <v>46141</v>
+        <v>46210</v>
       </c>
       <c r="D8" s="4">
-        <v>552606577</v>
+        <v>552857208</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F8" s="6">
         <v>46094</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K8" s="3">
         <v>46268</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>177</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <v>293</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-21</v>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <v>48</v>
       </c>
       <c r="O8" s="6">
         <v>46459</v>
@@ -4972,13 +4972,13 @@
         <v>1426.25</v>
       </c>
       <c r="AA8" s="7">
-        <v>1184.69</v>
+        <v>1223.6600000000001</v>
       </c>
       <c r="AB8" s="7">
-        <v>198.17</v>
+        <v>159.19999999999999</v>
       </c>
       <c r="AC8" s="6">
-        <v>46141</v>
+        <v>46210</v>
       </c>
       <c r="AD8" s="7">
         <v>43.39</v>
@@ -4987,19 +4987,19 @@
         <v>148</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="AG8" s="5"/>
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="4">
-        <v>559120100</v>
+        <v>559120090</v>
       </c>
       <c r="AK8" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM8" s="6">
         <v>46119</v>
@@ -5008,57 +5008,57 @@
         <v>53</v>
       </c>
       <c r="AO8" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>459</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C9" s="3">
-        <v>46210</v>
+        <v>46134</v>
       </c>
       <c r="D9" s="4">
-        <v>552857208</v>
+        <v>554160609</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9" s="6">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="K9" s="3">
         <v>46268</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>293</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>217</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>48</v>
+        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <v>-28</v>
       </c>
       <c r="O9" s="6">
-        <v>46459</v>
+        <v>46473</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>59</v>
@@ -5085,34 +5085,34 @@
         <v>49</v>
       </c>
       <c r="Z9" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA9" s="7">
-        <v>1223.6600000000001</v>
+        <v>1184.44</v>
       </c>
       <c r="AB9" s="7">
-        <v>159.19999999999999</v>
+        <v>148.02000000000001</v>
       </c>
       <c r="AC9" s="6">
-        <v>46210</v>
+        <v>46134</v>
       </c>
       <c r="AD9" s="7">
-        <v>43.39</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="AE9" s="4">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="4">
-        <v>559120090</v>
+        <v>559120425</v>
       </c>
       <c r="AK9" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>80</v>
@@ -5124,7 +5124,7 @@
         <v>53</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
@@ -5132,46 +5132,46 @@
         <v>459</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C10" s="3">
-        <v>46134</v>
+        <v>46268</v>
       </c>
       <c r="D10" s="4">
-        <v>554160609</v>
+        <v>555138984</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F10" s="6">
         <v>46108</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>57</v>
       </c>
       <c r="K10" s="3">
-        <v>46268</v>
+        <v>46254</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>191</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>351</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-28</v>
+        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <v>106</v>
       </c>
       <c r="O10" s="6">
         <v>46473</v>
@@ -5204,31 +5204,27 @@
         <v>1372.91</v>
       </c>
       <c r="AA10" s="7">
-        <v>1184.44</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="7">
-        <v>148.02000000000001</v>
-      </c>
-      <c r="AC10" s="6">
-        <v>46134</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="6"/>
       <c r="AD10" s="7">
-        <v>40.450000000000003</v>
+        <v>1372.91</v>
       </c>
       <c r="AE10" s="4">
         <v>134</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="AG10" s="5"/>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
-      <c r="AJ10" s="4">
-        <v>559120425</v>
-      </c>
+      <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="AL10" s="5" t="s">
         <v>80</v>
@@ -5240,27 +5236,27 @@
         <v>53</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>459</v>
+        <v>250</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C11" s="3">
-        <v>46268</v>
+        <v>46125</v>
       </c>
       <c r="D11" s="4">
-        <v>555138984</v>
+        <v>554403926</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F11" s="6">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>67</v>
@@ -5269,28 +5265,28 @@
         <v>67</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K11" s="3">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>191</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>194</v>
       </c>
       <c r="M11" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <v>208</v>
       </c>
       <c r="N11" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>106</v>
+        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <v>-37</v>
       </c>
       <c r="O11" s="6">
-        <v>46473</v>
+        <v>46476</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>59</v>
@@ -5317,7 +5313,7 @@
         <v>49</v>
       </c>
       <c r="Z11" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -5325,25 +5321,27 @@
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6"/>
+      <c r="AC11" s="6">
+        <v>46125</v>
+      </c>
       <c r="AD11" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE11" s="4">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="AM11" s="6">
         <v>46119</v>
@@ -5352,7 +5350,7 @@
         <v>53</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -5360,55 +5358,55 @@
         <v>250</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C12" s="3">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="D12" s="4">
-        <v>554403926</v>
+        <v>566722180</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F12" s="6">
-        <v>46111</v>
+        <v>46085</v>
       </c>
       <c r="G12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="J12" s="5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K12" s="3">
-        <v>46268</v>
+        <v>46231</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>194</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-107</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>217</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-37</v>
+        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <v>217</v>
       </c>
       <c r="O12" s="6">
-        <v>46476</v>
+        <v>46175</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="R12" s="5" t="s">
         <v>59</v>
@@ -5417,7 +5415,7 @@
         <v>48</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>48</v>
@@ -5426,10 +5424,10 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="Z12" s="7">
-        <v>1426.25</v>
+        <v>1769.18</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -5438,26 +5436,26 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46125</v>
+        <v>46134</v>
       </c>
       <c r="AD12" s="7">
-        <v>1426.25</v>
+        <v>1769.18</v>
       </c>
       <c r="AE12" s="4">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="AG12" s="5"/>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AM12" s="6">
         <v>46119</v>
@@ -5466,7 +5464,7 @@
         <v>53</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -5474,55 +5472,55 @@
         <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="C13" s="3">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="D13" s="4">
-        <v>566722180</v>
+        <v>551769931</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F13" s="6">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="K13" s="3">
-        <v>46231</v>
+        <v>46265</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-107</v>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v>-106</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" ref="N13:N24" ca="1" si="3">IF($C13="","",$C13+365-TODAY())</f>
-        <v>217</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="O13" s="6">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>59</v>
@@ -5540,10 +5538,10 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="Z13" s="7">
-        <v>1769.18</v>
+        <v>1372.91</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -5552,26 +5550,26 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="AD13" s="7">
-        <v>1769.18</v>
+        <v>1372.91</v>
       </c>
       <c r="AE13" s="4">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM13" s="6">
         <v>46119</v>
@@ -5580,66 +5578,66 @@
         <v>53</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>459</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="C14" s="3">
-        <v>46141</v>
+        <v>46196</v>
       </c>
       <c r="D14" s="4">
-        <v>551769931</v>
+        <v>551830492</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F14" s="6">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="K14" s="3">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-106</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-105</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>94</v>
       </c>
       <c r="N14" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>224</v>
+        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <v>279</v>
       </c>
       <c r="O14" s="6">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S14" s="5" t="s">
         <v>48</v>
@@ -5657,35 +5655,37 @@
         <v>49</v>
       </c>
       <c r="Z14" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA14" s="7">
-        <v>0</v>
+        <v>1223.69</v>
       </c>
       <c r="AB14" s="7">
-        <v>0</v>
+        <v>354.8</v>
       </c>
       <c r="AC14" s="6">
-        <v>46141</v>
+        <v>46196</v>
       </c>
       <c r="AD14" s="7">
-        <v>1372.91</v>
+        <v>-152.24</v>
       </c>
       <c r="AE14" s="4">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
-      <c r="AJ14" s="4"/>
+      <c r="AJ14" s="4">
+        <v>560056768</v>
+      </c>
       <c r="AK14" s="5" t="s">
         <v>94</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AM14" s="6">
         <v>46119</v>
@@ -5694,54 +5694,54 @@
         <v>53</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>459</v>
+        <v>250</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C15" s="3">
-        <v>46196</v>
+        <v>46121</v>
       </c>
       <c r="D15" s="4">
-        <v>551830492</v>
+        <v>551874008</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F15" s="6">
         <v>46087</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="K15" s="3">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O15="","",$O15-TODAY())</f>
         <v>-105</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>94</v>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v>204</v>
       </c>
       <c r="N15" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>279</v>
+        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <v>204</v>
       </c>
       <c r="O15" s="6">
         <v>46177</v>
@@ -5750,10 +5750,10 @@
         <v>112</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>48</v>
@@ -5774,34 +5774,32 @@
         <v>1426.25</v>
       </c>
       <c r="AA15" s="7">
-        <v>1223.69</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="7">
-        <v>354.8</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="6">
-        <v>46196</v>
+        <v>46121</v>
       </c>
       <c r="AD15" s="7">
-        <v>-152.24</v>
+        <v>1426.25</v>
       </c>
       <c r="AE15" s="4">
         <v>155</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
-      <c r="AJ15" s="4">
-        <v>560056768</v>
-      </c>
+      <c r="AJ15" s="4"/>
       <c r="AK15" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="AL15" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM15" s="6">
         <v>46119</v>
@@ -5810,7 +5808,7 @@
         <v>53</v>
       </c>
       <c r="AO15" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -5818,19 +5816,19 @@
         <v>250</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C16" s="3">
         <v>46121</v>
       </c>
       <c r="D16" s="4">
-        <v>551874008</v>
+        <v>552405449</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F16" s="6">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>117</v>
@@ -5842,25 +5840,25 @@
         <v>43</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K16" s="3">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-105</v>
+        <f ca="1">IF($O16="","",$O16-TODAY())</f>
+        <v>-100</v>
       </c>
       <c r="M16" s="12">
         <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
         <v>204</v>
       </c>
       <c r="N16" s="12">
-        <f t="shared" ca="1" si="3"/>
+        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
         <v>204</v>
       </c>
       <c r="O16" s="6">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>112</v>
@@ -5902,17 +5900,17 @@
         <v>1426.25</v>
       </c>
       <c r="AE16" s="4">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AF16" s="5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="AG16" s="5"/>
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="4"/>
       <c r="AK16" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="AL16" s="5" t="s">
         <v>80</v>
@@ -5924,66 +5922,66 @@
         <v>53</v>
       </c>
       <c r="AO16" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="C17" s="3">
-        <v>46121</v>
+        <v>46223</v>
       </c>
       <c r="D17" s="4">
-        <v>552405449</v>
+        <v>563362999</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F17" s="6">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>46257</v>
+        <v>46268</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-100</v>
+        <f ca="1">IF($O17="","",$O17-TODAY())</f>
+        <v>-98</v>
       </c>
       <c r="M17" s="12">
+        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
+        <v>121</v>
+      </c>
+      <c r="N17" s="12">
         <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>204</v>
-      </c>
-      <c r="N17" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>204</v>
+        <v>306</v>
       </c>
       <c r="O17" s="6">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S17" s="5" t="s">
         <v>48</v>
@@ -5994,7 +5992,9 @@
       <c r="U17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V17" s="5"/>
+      <c r="V17" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5" t="s">
@@ -6010,26 +6010,26 @@
         <v>0</v>
       </c>
       <c r="AC17" s="6">
-        <v>46121</v>
+        <v>46223</v>
       </c>
       <c r="AD17" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE17" s="4">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AF17" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG17" s="5"/>
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="4"/>
       <c r="AK17" s="5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="AL17" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AM17" s="6">
         <v>46119</v>
@@ -6038,66 +6038,66 @@
         <v>53</v>
       </c>
       <c r="AO17" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C18" s="3">
-        <v>46223</v>
+        <v>46135</v>
       </c>
       <c r="D18" s="4">
-        <v>563362999</v>
+        <v>552859864</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F18" s="6">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="K18" s="3">
         <v>46268</v>
       </c>
       <c r="L18" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-98</v>
+        <f ca="1">IF($O18="","",$O18-TODAY())</f>
+        <v>-95</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>121</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>218</v>
       </c>
       <c r="N18" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>306</v>
+        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <v>218</v>
       </c>
       <c r="O18" s="6">
-        <v>46184</v>
+        <v>46187</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S18" s="5" t="s">
         <v>48</v>
@@ -6108,9 +6108,7 @@
       <c r="U18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V18" s="5" t="s">
-        <v>134</v>
-      </c>
+      <c r="V18" s="5"/>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
       <c r="Y18" s="5" t="s">
@@ -6126,26 +6124,28 @@
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <v>46223</v>
+        <v>46135</v>
       </c>
       <c r="AD18" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE18" s="4">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AF18" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG18" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="AG18" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="4"/>
       <c r="AK18" s="5" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="AL18" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AM18" s="6">
         <v>46119</v>
@@ -6154,7 +6154,7 @@
         <v>53</v>
       </c>
       <c r="AO18" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
@@ -6162,58 +6162,58 @@
         <v>250</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C19" s="3">
-        <v>46135</v>
+        <v>46161</v>
       </c>
       <c r="D19" s="4">
-        <v>552859864</v>
+        <v>553133483</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F19" s="6">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K19" s="3">
         <v>46268</v>
       </c>
       <c r="L19" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-95</v>
+        <f ca="1">IF($O19="","",$O19-TODAY())</f>
+        <v>-93</v>
       </c>
       <c r="M19" s="12">
+        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
+        <v>59</v>
+      </c>
+      <c r="N19" s="12">
         <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
-        <v>218</v>
-      </c>
-      <c r="N19" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="O19" s="6">
-        <v>46187</v>
+        <v>46189</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S19" s="5" t="s">
         <v>48</v>
@@ -6240,28 +6240,26 @@
         <v>0</v>
       </c>
       <c r="AC19" s="6">
-        <v>46135</v>
+        <v>46161</v>
       </c>
       <c r="AD19" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE19" s="4">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG19" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="AG19" s="5"/>
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="4"/>
       <c r="AK19" s="5" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="AL19" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AM19" s="6">
         <v>46119</v>
@@ -6270,7 +6268,7 @@
         <v>53</v>
       </c>
       <c r="AO19" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -6278,46 +6276,46 @@
         <v>250</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C20" s="3">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="D20" s="4">
-        <v>553133483</v>
+        <v>553148506</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F20" s="6">
         <v>46099</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="K20" s="3">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O20="","",$O20-TODAY())</f>
         <v>-93</v>
       </c>
       <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>59</v>
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <v>250</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>244</v>
+        <f ca="1">IF($C20="","",$C20+365-TODAY())</f>
+        <v>250</v>
       </c>
       <c r="O20" s="6">
         <v>46189</v>
@@ -6326,10 +6324,10 @@
         <v>112</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S20" s="5" t="s">
         <v>48</v>
@@ -6347,7 +6345,7 @@
         <v>49</v>
       </c>
       <c r="Z20" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AA20" s="7">
         <v>0</v>
@@ -6356,55 +6354,57 @@
         <v>0</v>
       </c>
       <c r="AC20" s="6">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="AD20" s="7">
-        <v>1426.25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE20" s="4">
         <v>143</v>
       </c>
       <c r="AF20" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="AG20" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="4"/>
       <c r="AK20" s="5" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AL20" s="5" t="s">
         <v>62</v>
       </c>
       <c r="AM20" s="6">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="AN20" s="5" t="s">
         <v>53</v>
       </c>
       <c r="AO20" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C21" s="3">
-        <v>46167</v>
+        <v>46185</v>
       </c>
       <c r="D21" s="4">
-        <v>553148506</v>
+        <v>553362911</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F21" s="6">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>117</v>
@@ -6416,25 +6416,25 @@
         <v>43</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="K21" s="3">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-93</v>
+        <f ca="1">IF($O21="","",$O21-TODAY())</f>
+        <v>-91</v>
       </c>
       <c r="M21" s="12">
         <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>250</v>
+        <f ca="1">IF($C21="","",$C21+365-TODAY())</f>
+        <v>268</v>
       </c>
       <c r="O21" s="6">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>112</v>
@@ -6461,93 +6461,91 @@
         <v>49</v>
       </c>
       <c r="Z21" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA21" s="7">
-        <v>0</v>
+        <v>1245.54</v>
       </c>
       <c r="AB21" s="7">
-        <v>0</v>
+        <v>361.42</v>
       </c>
       <c r="AC21" s="6">
-        <v>46167</v>
+        <v>46185</v>
       </c>
       <c r="AD21" s="7">
-        <v>1372.91</v>
+        <v>-180.71</v>
       </c>
       <c r="AE21" s="4">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG21" s="5" t="s">
-        <v>60</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="AG21" s="5"/>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="4"/>
       <c r="AK21" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AL21" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM21" s="6">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="AN21" s="5" t="s">
         <v>53</v>
       </c>
       <c r="AO21" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>446</v>
+        <v>250</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C22" s="3">
-        <v>46185</v>
+        <v>46124</v>
       </c>
       <c r="D22" s="4">
-        <v>553362911</v>
+        <v>553498942</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F22" s="6">
         <v>46101</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="K22" s="3">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="L22" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O22="","",$O22-TODAY())</f>
         <v>-91</v>
       </c>
       <c r="M22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>268</v>
+        <v>207</v>
       </c>
       <c r="N22" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>268</v>
+        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
+        <v>207</v>
       </c>
       <c r="O22" s="6">
         <v>46191</v>
@@ -6556,7 +6554,7 @@
         <v>112</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="R22" s="5" t="s">
         <v>59</v>
@@ -6580,16 +6578,16 @@
         <v>1426.25</v>
       </c>
       <c r="AA22" s="7">
-        <v>1245.54</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="7">
-        <v>361.42</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="6">
-        <v>46185</v>
+        <v>46124</v>
       </c>
       <c r="AD22" s="7">
-        <v>-180.71</v>
+        <v>1426.25</v>
       </c>
       <c r="AE22" s="4">
         <v>141</v>
@@ -6602,7 +6600,7 @@
       <c r="AI22" s="5"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="5" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="AL22" s="5" t="s">
         <v>80</v>
@@ -6614,63 +6612,63 @@
         <v>53</v>
       </c>
       <c r="AO22" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="C23" s="3">
-        <v>46124</v>
+        <v>46141</v>
       </c>
       <c r="D23" s="4">
-        <v>553498942</v>
+        <v>555169750</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F23" s="6">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="K23" s="3">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="L23" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-91</v>
+        <f ca="1">IF($O23="","",$O23-TODAY())</f>
+        <v>-88</v>
       </c>
       <c r="M23" s="12">
         <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>207</v>
+        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="O23" s="6">
-        <v>46191</v>
+        <v>46194</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="R23" s="5" t="s">
         <v>59</v>
@@ -6691,7 +6689,7 @@
         <v>49</v>
       </c>
       <c r="Z23" s="7">
-        <v>1426.25</v>
+        <v>396.27</v>
       </c>
       <c r="AA23" s="7">
         <v>0</v>
@@ -6700,35 +6698,37 @@
         <v>0</v>
       </c>
       <c r="AC23" s="6">
-        <v>46124</v>
+        <v>46141</v>
       </c>
       <c r="AD23" s="7">
-        <v>1426.25</v>
+        <v>396.27</v>
       </c>
       <c r="AE23" s="4">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AF23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG23" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="AG23" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="4"/>
       <c r="AK23" s="5" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="AL23" s="5" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="AM23" s="6">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="AN23" s="5" t="s">
         <v>53</v>
       </c>
       <c r="AO23" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
@@ -6736,64 +6736,64 @@
         <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C24" s="3">
-        <v>46141</v>
+        <v>46123</v>
       </c>
       <c r="D24" s="4">
-        <v>555169750</v>
+        <v>554246495</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F24" s="6">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K24" s="3">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="L24" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-88</v>
+        <f ca="1">IF($O24="","",$O24-TODAY())</f>
+        <v>-86</v>
       </c>
       <c r="M24" s="12">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>224</v>
+        <f ca="1">IF($F24="","",$F24+90-TODAY())</f>
+        <v>-86</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" ca="1" si="3"/>
-        <v>224</v>
+        <f ca="1">IF($C24="","",$C24+60-TODAY())</f>
+        <v>-99</v>
       </c>
       <c r="O24" s="6">
-        <v>46194</v>
+        <v>46196</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>48</v>
@@ -6805,111 +6805,111 @@
         <v>49</v>
       </c>
       <c r="Z24" s="7">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="AA24" s="7">
-        <v>0</v>
+        <v>883.53</v>
       </c>
       <c r="AB24" s="7">
-        <v>0</v>
+        <v>121.45</v>
       </c>
       <c r="AC24" s="6">
-        <v>46141</v>
+        <v>46123</v>
       </c>
       <c r="AD24" s="7">
-        <v>396.27</v>
+        <v>25</v>
       </c>
       <c r="AE24" s="4">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF24" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AG24" s="5" t="s">
-        <v>150</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="AG24" s="5"/>
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
-      <c r="AJ24" s="4"/>
+      <c r="AJ24" s="4">
+        <v>557570817</v>
+      </c>
       <c r="AK24" s="5" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="AL24" s="5" t="s">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="AM24" s="6">
-        <v>46105</v>
+        <v>46119</v>
       </c>
       <c r="AN24" s="5" t="s">
         <v>53</v>
       </c>
       <c r="AO24" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C25" s="3">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="D25" s="4">
-        <v>554246495</v>
+        <v>554088972</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F25" s="6">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="K25" s="3">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="L25" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-86</v>
+        <f ca="1">IF($O25="","",$O25-TODAY())</f>
+        <v>-84</v>
       </c>
       <c r="M25" s="12">
-        <f ca="1">IF($F25="","",$F25+90-TODAY())</f>
-        <v>-86</v>
+        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+60-TODAY())</f>
-        <v>-99</v>
+        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="O25" s="6">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T25" s="5" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="U25" s="5" t="s">
         <v>48</v>
@@ -6921,37 +6921,35 @@
         <v>49</v>
       </c>
       <c r="Z25" s="7">
-        <v>1029.98</v>
+        <v>1372.91</v>
       </c>
       <c r="AA25" s="7">
-        <v>883.53</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="7">
-        <v>121.45</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="6">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="AD25" s="7">
-        <v>25</v>
+        <v>1372.91</v>
       </c>
       <c r="AE25" s="4">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF25" s="5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="AG25" s="5"/>
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
-      <c r="AJ25" s="4">
-        <v>557570817</v>
-      </c>
+      <c r="AJ25" s="4"/>
       <c r="AK25" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AL25" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AM25" s="6">
         <v>46119</v>
@@ -6960,7 +6958,7 @@
         <v>53</v>
       </c>
       <c r="AO25" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
@@ -6968,46 +6966,46 @@
         <v>250</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="C26" s="3">
-        <v>46141</v>
+        <v>46197</v>
       </c>
       <c r="D26" s="4">
-        <v>554088972</v>
+        <v>563362114</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F26" s="6">
         <v>46108</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="K26" s="3">
-        <v>46266</v>
+        <v>46148</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O26="","",$O26-TODAY())</f>
         <v>-84</v>
       </c>
       <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>224</v>
+        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
+        <v>95</v>
       </c>
       <c r="N26" s="12">
         <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="O26" s="6">
         <v>46198</v>
@@ -7016,10 +7014,10 @@
         <v>112</v>
       </c>
       <c r="Q26" s="5" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S26" s="5" t="s">
         <v>48</v>
@@ -7030,14 +7028,16 @@
       <c r="U26" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V26" s="5"/>
+      <c r="V26" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z26" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AA26" s="7">
         <v>0</v>
@@ -7046,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="AC26" s="6">
-        <v>46141</v>
+        <v>46197</v>
       </c>
       <c r="AD26" s="7">
-        <v>1372.91</v>
+        <v>1426.25</v>
       </c>
       <c r="AE26" s="4">
         <v>134</v>
@@ -7074,63 +7074,63 @@
         <v>53</v>
       </c>
       <c r="AO26" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C27" s="3">
-        <v>46197</v>
+        <v>46184</v>
       </c>
       <c r="D27" s="4">
-        <v>563362114</v>
+        <v>553283455</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F27" s="6">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="K27" s="3">
-        <v>46148</v>
+        <v>46268</v>
       </c>
       <c r="L27" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-84</v>
+        <f ca="1">IF($O27="","",$O27-TODAY())</f>
+        <v>-62</v>
       </c>
       <c r="M27" s="12">
         <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>280</v>
+        <f ca="1">IF($C27="","",$C27+180-TODAY())</f>
+        <v>82</v>
       </c>
       <c r="O27" s="6">
-        <v>46198</v>
+        <v>46220</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="R27" s="5" t="s">
         <v>45</v>
@@ -7139,14 +7139,12 @@
         <v>48</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="U27" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V27" s="5" t="s">
-        <v>134</v>
-      </c>
+      <c r="V27" s="5"/>
       <c r="W27" s="5"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5" t="s">
@@ -7162,26 +7160,26 @@
         <v>0</v>
       </c>
       <c r="AC27" s="6">
-        <v>46197</v>
+        <v>46184</v>
       </c>
       <c r="AD27" s="7">
         <v>1426.25</v>
       </c>
       <c r="AE27" s="4">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="AG27" s="5"/>
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AL27" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM27" s="6">
         <v>46119</v>
@@ -7190,72 +7188,72 @@
         <v>53</v>
       </c>
       <c r="AO27" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C28" s="3">
-        <v>46184</v>
+        <v>46128</v>
       </c>
       <c r="D28" s="4">
-        <v>553283455</v>
+        <v>554404221</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F28" s="6">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="K28" s="3">
         <v>46268</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-62</v>
+        <f ca="1">IF($O28="","",$O28-TODAY())</f>
+        <v>-50</v>
       </c>
       <c r="M28" s="12">
-        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
-        <v>82</v>
+        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
+        <v>211</v>
       </c>
       <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+180-TODAY())</f>
-        <v>82</v>
+        <f ca="1">IF($C28="","",$C28+90-TODAY())</f>
+        <v>-64</v>
       </c>
       <c r="O28" s="6">
-        <v>46220</v>
+        <v>46232</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>70</v>
       </c>
       <c r="Q28" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S28" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="U28" s="5" t="s">
         <v>48</v>
@@ -7267,7 +7265,7 @@
         <v>49</v>
       </c>
       <c r="Z28" s="7">
-        <v>1426.25</v>
+        <v>976.64</v>
       </c>
       <c r="AA28" s="7">
         <v>0</v>
@@ -7276,26 +7274,26 @@
         <v>0</v>
       </c>
       <c r="AC28" s="6">
-        <v>46184</v>
+        <v>46128</v>
       </c>
       <c r="AD28" s="7">
-        <v>1426.25</v>
+        <v>976.64</v>
       </c>
       <c r="AE28" s="4">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="AF28" s="5" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="AG28" s="5"/>
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AL28" s="5" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="AM28" s="6">
         <v>46119</v>
@@ -7304,7 +7302,7 @@
         <v>53</v>
       </c>
       <c r="AO28" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
@@ -7312,68 +7310,50 @@
         <v>250</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C29" s="3">
         <v>46128</v>
       </c>
       <c r="D29" s="4">
-        <v>554404221</v>
+        <v>553124954</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F29" s="6">
-        <v>46112</v>
+        <v>46099</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="K29" s="3">
-        <v>46268</v>
-      </c>
-      <c r="L29" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>211</v>
-      </c>
-      <c r="N29" s="12">
-        <f ca="1">IF($C29="","",$C29+90-TODAY())</f>
-        <v>-64</v>
-      </c>
-      <c r="O29" s="6">
-        <v>46232</v>
-      </c>
-      <c r="P29" s="5" t="s">
-        <v>70</v>
-      </c>
+        <v>46269</v>
+      </c>
+      <c r="L29" s="12" t="str">
+        <f ca="1">IF($O29="","",$O29-TODAY())</f>
+        <v/>
+      </c>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="5"/>
       <c r="Q29" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="R29" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T29" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="U29" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
@@ -7381,7 +7361,7 @@
         <v>49</v>
       </c>
       <c r="Z29" s="7">
-        <v>976.64</v>
+        <v>1372.91</v>
       </c>
       <c r="AA29" s="7">
         <v>0</v>
@@ -7393,10 +7373,10 @@
         <v>46128</v>
       </c>
       <c r="AD29" s="7">
-        <v>976.64</v>
+        <v>1372.91</v>
       </c>
       <c r="AE29" s="4">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>71</v>
@@ -7406,10 +7386,10 @@
       <c r="AI29" s="5"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="5" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="AL29" s="5" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="AM29" s="6">
         <v>46119</v>
@@ -7418,45 +7398,45 @@
         <v>53</v>
       </c>
       <c r="AO29" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C30" s="3">
-        <v>46128</v>
+        <v>46164</v>
       </c>
       <c r="D30" s="4">
-        <v>553124954</v>
+        <v>553577987</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F30" s="6">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>43</v>
+        <v>178</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="K30" s="3">
         <v>46269</v>
       </c>
       <c r="L30" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O30="","",$O30-TODAY())</f>
         <v/>
       </c>
       <c r="M30" s="12"/>
@@ -7474,25 +7454,25 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="Z30" s="7">
-        <v>1372.91</v>
+        <v>1822.52</v>
       </c>
       <c r="AA30" s="7">
-        <v>0</v>
+        <v>1549.83</v>
       </c>
       <c r="AB30" s="7">
-        <v>0</v>
+        <v>217.27</v>
       </c>
       <c r="AC30" s="6">
-        <v>46128</v>
+        <v>46164</v>
       </c>
       <c r="AD30" s="7">
-        <v>1372.91</v>
+        <v>55.42</v>
       </c>
       <c r="AE30" s="4">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AF30" s="5" t="s">
         <v>71</v>
@@ -7500,12 +7480,14 @@
       <c r="AG30" s="5"/>
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
-      <c r="AJ30" s="4"/>
+      <c r="AJ30" s="4">
+        <v>557766116</v>
+      </c>
       <c r="AK30" s="5" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="AL30" s="5" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="AM30" s="6">
         <v>46119</v>
@@ -7514,204 +7496,12 @@
         <v>53</v>
       </c>
       <c r="AO30" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C31" s="3">
-        <v>46164</v>
-      </c>
-      <c r="D31" s="4">
-        <v>553577987</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F31" s="6">
-        <v>46104</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="3">
-        <v>46269</v>
-      </c>
-      <c r="L31" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z31" s="7">
-        <v>1822.52</v>
-      </c>
-      <c r="AA31" s="7">
-        <v>1549.83</v>
-      </c>
-      <c r="AB31" s="7">
-        <v>217.27</v>
-      </c>
-      <c r="AC31" s="6">
-        <v>46164</v>
-      </c>
-      <c r="AD31" s="7">
-        <v>55.42</v>
-      </c>
-      <c r="AE31" s="4">
-        <v>138</v>
-      </c>
-      <c r="AF31" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG31" s="5"/>
-      <c r="AH31" s="5"/>
-      <c r="AI31" s="5"/>
-      <c r="AJ31" s="4">
-        <v>557766116</v>
-      </c>
-      <c r="AK31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AL31" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM31" s="6">
-        <v>46119</v>
-      </c>
-      <c r="AN31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO31" s="5" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C32" s="3">
-        <v>46245</v>
-      </c>
-      <c r="D32" s="4">
-        <v>554062261</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46108</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K32" s="3">
-        <v>46260</v>
-      </c>
-      <c r="L32" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z32" s="7">
-        <v>1426.25</v>
-      </c>
-      <c r="AA32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="7">
-        <v>1426.25</v>
-      </c>
-      <c r="AE32" s="4">
-        <v>134</v>
-      </c>
-      <c r="AF32" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG32" s="5"/>
-      <c r="AH32" s="5"/>
-      <c r="AI32" s="5"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL32" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM32" s="6">
-        <v>46119</v>
-      </c>
-      <c r="AN32" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO32" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="L2:L32">
+  <autoFilter ref="A1:AO30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:L30">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -7728,7 +7518,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M32">
+  <conditionalFormatting sqref="M2:M30">
     <cfRule type="expression" dxfId="94" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -7745,7 +7535,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N32">
+  <conditionalFormatting sqref="N2:N30">
     <cfRule type="expression" dxfId="89" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -7762,7 +7552,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U32">
+  <conditionalFormatting sqref="O2:U30">
     <cfRule type="expression" dxfId="84" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -7780,7 +7570,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A32" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9179,7 +8969,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO4"/>
+  <dimension ref="A1:AO3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9471,91 +9261,84 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="C3" s="3">
         <v>46132</v>
       </c>
       <c r="D3" s="4">
-        <v>555069394</v>
+        <v>555069563</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F3" s="6">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="K3" s="3">
-        <v>46278</v>
-      </c>
-      <c r="L3" s="12">
+        <v>46197</v>
+      </c>
+      <c r="L3" s="12" t="str">
         <f ca="1">IF($O3="","",$O3-TODAY())</f>
-        <v>-103</v>
-      </c>
-      <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>215</v>
-      </c>
+        <v/>
+      </c>
+      <c r="M3" s="12"/>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>215</v>
-      </c>
-      <c r="O3" s="6">
-        <v>46179</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>112</v>
-      </c>
+        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <v>30</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="5"/>
       <c r="Q3" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
       <c r="T3" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
+      <c r="V3" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="X3" s="5"/>
       <c r="Y3" s="5" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
       <c r="Z3" s="7">
-        <v>49162.82</v>
+        <v>70557.69</v>
       </c>
       <c r="AA3" s="7">
-        <v>42467.38</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="7">
-        <v>2458.9299999999998</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="6">
         <v>46132</v>
       </c>
       <c r="AD3" s="7">
-        <v>4236.51</v>
+        <v>70557.69</v>
       </c>
       <c r="AE3" s="4">
         <v>152</v>
@@ -9570,9 +9353,7 @@
         <v>268</v>
       </c>
       <c r="AI3" s="5"/>
-      <c r="AJ3" s="4">
-        <v>560554996</v>
-      </c>
+      <c r="AJ3" s="4"/>
       <c r="AK3" s="5" t="s">
         <v>260</v>
       </c>
@@ -9586,123 +9367,12 @@
         <v>262</v>
       </c>
       <c r="AO3" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46132</v>
-      </c>
-      <c r="D4" s="4">
-        <v>555069563</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46090</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="K4" s="3">
-        <v>46197</v>
-      </c>
-      <c r="L4" s="12" t="str">
-        <f ca="1">IF($O4="","",$O4-TODAY())</f>
-        <v/>
-      </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
-        <v>30</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="Z4" s="7">
-        <v>70557.69</v>
-      </c>
-      <c r="AA4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>46132</v>
-      </c>
-      <c r="AD4" s="7">
-        <v>70557.69</v>
-      </c>
-      <c r="AE4" s="4">
-        <v>152</v>
-      </c>
-      <c r="AF4" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AL4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM4" s="6">
-        <v>46119</v>
-      </c>
-      <c r="AN4" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AO4" s="5" t="s">
         <v>278</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO4" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="L2:L4">
+  <autoFilter ref="A1:AO3" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:L3">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -9719,7 +9389,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M4">
+  <conditionalFormatting sqref="M2:M3">
     <cfRule type="expression" dxfId="54" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -9736,7 +9406,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N4">
+  <conditionalFormatting sqref="N2:N3">
     <cfRule type="expression" dxfId="49" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -9753,7 +9423,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U4">
+  <conditionalFormatting sqref="O2:U3">
     <cfRule type="expression" dxfId="44" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -9771,7 +9441,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A4" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9782,7 +9452,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO16"/>
+  <dimension ref="A1:AO14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9983,15 +9653,15 @@
         <v>46279</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L16" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>166</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M8" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
         <v>190</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N8" ca="1" si="2">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
         <v>-55</v>
       </c>
       <c r="O2" s="6">
@@ -10099,15 +9769,15 @@
         <v>46279</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>168</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
         <v>286</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
         <v>41</v>
       </c>
       <c r="O3" s="6">
@@ -10186,25 +9856,25 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>446</v>
+        <v>459</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>487</v>
       </c>
       <c r="C4" s="3">
-        <v>46128</v>
+        <v>46108</v>
       </c>
       <c r="D4" s="4">
-        <v>553719866</v>
+        <v>553223068</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>74</v>
+        <v>294</v>
       </c>
       <c r="F4" s="6">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>67</v>
@@ -10216,22 +9886,22 @@
         <v>292</v>
       </c>
       <c r="K4" s="3">
-        <v>46142</v>
+        <v>46266</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>182</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>211</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-34</v>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <v>-54</v>
       </c>
       <c r="O4" s="6">
-        <v>46459</v>
+        <v>46464</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>59</v>
@@ -10261,65 +9931,63 @@
         <v>2493.33</v>
       </c>
       <c r="AA4" s="7">
-        <v>2340.79</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="7">
-        <v>121.54</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46128</v>
+        <v>46108</v>
       </c>
       <c r="AD4" s="7">
-        <v>31</v>
+        <v>2493.33</v>
       </c>
       <c r="AE4" s="4">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
-      <c r="AJ4" s="4">
-        <v>557765461</v>
-      </c>
+      <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="AM4" s="6">
-        <v>46113</v>
+        <v>46101</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO4" s="5" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>459</v>
+        <v>250</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C5" s="3">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="D5" s="4">
-        <v>553223068</v>
+        <v>555372244</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F5" s="6">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>67</v>
@@ -10331,25 +9999,25 @@
         <v>75</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="K5" s="3">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>182</v>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>187</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>286</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-54</v>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <v>41</v>
       </c>
       <c r="O5" s="6">
-        <v>46464</v>
+        <v>46469</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>59</v>
@@ -10369,14 +10037,16 @@
       <c r="U5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V5" s="5"/>
+      <c r="V5" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z5" s="7">
-        <v>2493.33</v>
+        <v>19949.23</v>
       </c>
       <c r="AA5" s="7">
         <v>0</v>
@@ -10385,87 +10055,91 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46108</v>
+        <v>46203</v>
       </c>
       <c r="AD5" s="7">
-        <v>2493.33</v>
+        <v>19949.23</v>
       </c>
       <c r="AE5" s="4">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
+        <v>304</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="AM5" s="6">
-        <v>46101</v>
+        <v>46197</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>459</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C6" s="3">
-        <v>46203</v>
+        <v>46122</v>
       </c>
       <c r="D6" s="4">
-        <v>555372244</v>
+        <v>553825634</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F6" s="6">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="K6" s="3">
         <v>46279</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>187</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>189</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>205</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>41</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>-40</v>
       </c>
       <c r="O6" s="6">
-        <v>46469</v>
+        <v>46471</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>59</v>
@@ -10485,59 +10159,53 @@
       <c r="U6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="V6" s="5"/>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z6" s="7">
-        <v>19949.23</v>
+        <v>2493.33</v>
       </c>
       <c r="AA6" s="7">
-        <v>0</v>
+        <v>2351.73</v>
       </c>
       <c r="AB6" s="7">
-        <v>0</v>
+        <v>110.6</v>
       </c>
       <c r="AC6" s="6">
-        <v>46203</v>
+        <v>46122</v>
       </c>
       <c r="AD6" s="7">
-        <v>19949.23</v>
+        <v>31</v>
       </c>
       <c r="AE6" s="4">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="AG6" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="AH6" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AI6" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="AJ6" s="4"/>
+        <v>307</v>
+      </c>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="4">
+        <v>557571095</v>
+      </c>
       <c r="AK6" s="5" t="s">
-        <v>290</v>
+        <v>94</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="AM6" s="6">
-        <v>46197</v>
+        <v>46107</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
@@ -10548,46 +10216,46 @@
         <v>490</v>
       </c>
       <c r="C7" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="D7" s="4">
-        <v>553825634</v>
+        <v>554186385</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F7" s="6">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>97</v>
+        <v>310</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>97</v>
+        <v>310</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="K7" s="3">
         <v>46279</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>189</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>191</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>205</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>209</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-40</v>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <v>-36</v>
       </c>
       <c r="O7" s="6">
-        <v>46471</v>
+        <v>46473</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>59</v>
@@ -10607,171 +10275,173 @@
       <c r="U7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V7" s="5"/>
+      <c r="V7" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z7" s="7">
-        <v>2493.33</v>
+        <v>5614.63</v>
       </c>
       <c r="AA7" s="7">
-        <v>2351.73</v>
+        <v>4889.05</v>
       </c>
       <c r="AB7" s="7">
-        <v>110.6</v>
+        <v>578.1</v>
       </c>
       <c r="AC7" s="6">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="AD7" s="7">
-        <v>31</v>
+        <v>147.47999999999999</v>
       </c>
       <c r="AE7" s="4">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="4">
-        <v>557571095</v>
+        <v>557570916</v>
       </c>
       <c r="AK7" s="5" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="AM7" s="6">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>308</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>459</v>
+        <v>250</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C8" s="3">
-        <v>46126</v>
+        <v>46204</v>
       </c>
       <c r="D8" s="4">
-        <v>554186385</v>
+        <v>552284225</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F8" s="6">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>67</v>
+        <v>314</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="K8" s="3">
-        <v>46279</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="K8" s="3"/>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>191</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>-107</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>209</v>
+        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <v>-107</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
-        <v>-36</v>
+        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <v>102</v>
       </c>
       <c r="O8" s="6">
-        <v>46473</v>
+        <v>46175</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>69</v>
+        <v>316</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V8" s="5" t="s">
-        <v>276</v>
-      </c>
+      <c r="V8" s="5"/>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z8" s="7">
-        <v>5614.63</v>
+        <v>1433.32</v>
       </c>
       <c r="AA8" s="7">
-        <v>4889.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="7">
-        <v>578.1</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="6">
-        <v>46126</v>
+        <v>46204</v>
       </c>
       <c r="AD8" s="7">
-        <v>147.47999999999999</v>
+        <v>1433.32</v>
       </c>
       <c r="AE8" s="4">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="AG8" s="5"/>
-      <c r="AH8" s="5"/>
-      <c r="AI8" s="5"/>
-      <c r="AJ8" s="4">
-        <v>557570916</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="AG8" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI8" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>146</v>
+        <v>290</v>
       </c>
       <c r="AL8" s="5" t="s">
         <v>261</v>
       </c>
       <c r="AM8" s="6">
-        <v>46112</v>
+        <v>46197</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO8" s="5" t="s">
-        <v>207</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
@@ -10779,53 +10449,55 @@
         <v>250</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C9" s="3">
-        <v>46204</v>
+        <v>46097</v>
       </c>
       <c r="D9" s="4">
-        <v>552284225</v>
+        <v>551964467</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F9" s="6">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>314</v>
+        <v>154</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>314</v>
+        <v>154</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="K9" s="3"/>
+        <v>320</v>
+      </c>
+      <c r="K9" s="3">
+        <v>46279</v>
+      </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-107</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>-105</v>
       </c>
       <c r="M9" s="12">
         <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
-        <v>-107</v>
+        <v>-105</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>102</v>
+        <f ca="1">IF($C9="","",$C9+60-TODAY())</f>
+        <v>-125</v>
       </c>
       <c r="O9" s="6">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>316</v>
+        <v>156</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>112</v>
@@ -10834,7 +10506,7 @@
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>48</v>
@@ -10846,7 +10518,7 @@
         <v>49</v>
       </c>
       <c r="Z9" s="7">
-        <v>1433.32</v>
+        <v>7623.07</v>
       </c>
       <c r="AA9" s="7">
         <v>0</v>
@@ -10855,88 +10527,80 @@
         <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46204</v>
+        <v>46097</v>
       </c>
       <c r="AD9" s="7">
-        <v>1433.32</v>
+        <v>7623.07</v>
       </c>
       <c r="AE9" s="4">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="AI9" s="5" t="s">
-        <v>317</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>290</v>
+        <v>146</v>
       </c>
       <c r="AL9" s="5" t="s">
         <v>261</v>
       </c>
       <c r="AM9" s="6">
-        <v>46197</v>
+        <v>46091</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>250</v>
+        <v>446</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
       <c r="C10" s="3">
-        <v>46097</v>
+        <v>46203</v>
       </c>
       <c r="D10" s="4">
-        <v>551964467</v>
+        <v>553643849</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F10" s="6">
         <v>46087</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="K10" s="3">
-        <v>46279</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>-105</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
-        <v>-105</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>286</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+60-TODAY())</f>
-        <v>-125</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>286</v>
       </c>
       <c r="O10" s="6">
         <v>46177</v>
@@ -10945,28 +10609,30 @@
         <v>112</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V10" s="5"/>
+      <c r="V10" s="5" t="s">
+        <v>324</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z10" s="7">
-        <v>7623.07</v>
+        <v>18400.34</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -10974,99 +10640,101 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6">
-        <v>46097</v>
-      </c>
+      <c r="AC10" s="6"/>
       <c r="AD10" s="7">
-        <v>7623.07</v>
+        <v>18400.34</v>
       </c>
       <c r="AE10" s="4">
         <v>155</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG10" s="5"/>
+        <v>325</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>326</v>
+      </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>146</v>
+        <v>327</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="AM10" s="6">
-        <v>46091</v>
+        <v>46197</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>446</v>
+        <v>250</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
       <c r="C11" s="3">
-        <v>46203</v>
+        <v>46108</v>
       </c>
       <c r="D11" s="4">
-        <v>553643849</v>
+        <v>553652690</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F11" s="6">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="K11" s="3"/>
+        <v>331</v>
+      </c>
+      <c r="K11" s="3">
+        <v>46265</v>
+      </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-105</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-99</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
+        <v>-99</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($C11="","",$C11+60-TODAY())</f>
+        <v>-114</v>
       </c>
       <c r="O11" s="6">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>48</v>
@@ -11088,18 +10756,20 @@
       <c r="AB11" s="7">
         <v>0</v>
       </c>
-      <c r="AC11" s="6"/>
+      <c r="AC11" s="6">
+        <v>46108</v>
+      </c>
       <c r="AD11" s="7">
         <v>18400.34</v>
       </c>
       <c r="AE11" s="4">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>325</v>
+        <v>199</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
@@ -11111,13 +10781,13 @@
         <v>328</v>
       </c>
       <c r="AM11" s="6">
-        <v>46197</v>
+        <v>46105</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -11125,16 +10795,16 @@
         <v>250</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C12" s="3">
-        <v>46108</v>
+        <v>46220</v>
       </c>
       <c r="D12" s="4">
-        <v>553652690</v>
+        <v>553656838</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F12" s="6">
         <v>46093</v>
@@ -11149,13 +10819,13 @@
         <v>43</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K12" s="3">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v>-99</v>
       </c>
       <c r="M12" s="12">
@@ -11164,7 +10834,7 @@
       </c>
       <c r="N12" s="12">
         <f ca="1">IF($C12="","",$C12+60-TODAY())</f>
-        <v>-114</v>
+        <v>-2</v>
       </c>
       <c r="O12" s="6">
         <v>46183</v>
@@ -11187,16 +10857,14 @@
       <c r="U12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="V12" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="V12" s="5"/>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="5" t="s">
         <v>49</v>
       </c>
       <c r="Z12" s="7">
-        <v>18400.34</v>
+        <v>12650.96</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -11205,10 +10873,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46108</v>
+        <v>46220</v>
       </c>
       <c r="AD12" s="7">
-        <v>18400.34</v>
+        <v>12650.96</v>
       </c>
       <c r="AE12" s="4">
         <v>149</v>
@@ -11217,7 +10885,7 @@
         <v>199</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
@@ -11235,7 +10903,7 @@
         <v>282</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -11243,46 +10911,46 @@
         <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C13" s="3">
-        <v>46220</v>
+        <v>46127</v>
       </c>
       <c r="D13" s="4">
-        <v>553656838</v>
+        <v>555351211</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F13" s="6">
         <v>46093</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K13" s="3">
         <v>46279</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
         <v>-99</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($F13="","",$F13+90-TODAY())</f>
-        <v>-99</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>25</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+60-TODAY())</f>
-        <v>-2</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>210</v>
       </c>
       <c r="O13" s="6">
         <v>46183</v>
@@ -11291,16 +10959,16 @@
         <v>112</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>48</v>
@@ -11312,7 +10980,7 @@
         <v>49</v>
       </c>
       <c r="Z13" s="7">
-        <v>12650.96</v>
+        <v>8277.57</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -11321,93 +10989,93 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46220</v>
+        <v>46127</v>
       </c>
       <c r="AD13" s="7">
-        <v>12650.96</v>
+        <v>8277.57</v>
       </c>
       <c r="AE13" s="4">
         <v>149</v>
       </c>
       <c r="AF13" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="AG13" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>336</v>
       </c>
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>328</v>
+        <v>261</v>
       </c>
       <c r="AM13" s="6">
-        <v>46105</v>
+        <v>46120</v>
       </c>
       <c r="AN13" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>459</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C14" s="3">
-        <v>46127</v>
+        <v>46163</v>
       </c>
       <c r="D14" s="4">
-        <v>555351211</v>
+        <v>553378154</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F14" s="6">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>122</v>
+        <v>348</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>122</v>
+        <v>348</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="K14" s="3">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-99</v>
+        <f ca="1">IF($O14="","",$O14-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="M14" s="12">
         <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
-        <v>210</v>
+        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <v>61</v>
       </c>
       <c r="O14" s="6">
-        <v>46183</v>
+        <v>46221</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>45</v>
@@ -11416,7 +11084,7 @@
         <v>48</v>
       </c>
       <c r="T14" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>48</v>
@@ -11428,7 +11096,7 @@
         <v>49</v>
       </c>
       <c r="Z14" s="7">
-        <v>8277.57</v>
+        <v>7623.07</v>
       </c>
       <c r="AA14" s="7">
         <v>0</v>
@@ -11437,278 +11105,40 @@
         <v>0</v>
       </c>
       <c r="AC14" s="6">
-        <v>46127</v>
+        <v>46163</v>
       </c>
       <c r="AD14" s="7">
-        <v>8277.57</v>
+        <v>7623.07</v>
       </c>
       <c r="AE14" s="4">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AG14" s="5" t="s">
-        <v>199</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="AG14" s="5"/>
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="4"/>
       <c r="AK14" s="5" t="s">
-        <v>281</v>
+        <v>94</v>
       </c>
       <c r="AL14" s="5" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="AM14" s="6">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="AN14" s="5" t="s">
         <v>282</v>
       </c>
       <c r="AO14" s="5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="C15" s="3">
-        <v>46101</v>
-      </c>
-      <c r="D15" s="4">
-        <v>553172544</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46097</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="K15" s="3">
-        <v>46276</v>
-      </c>
-      <c r="L15" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-95</v>
-      </c>
-      <c r="M15" s="12">
-        <f ca="1">IF($F15="","",$F15+90-TODAY())</f>
-        <v>-95</v>
-      </c>
-      <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+60-TODAY())</f>
-        <v>-121</v>
-      </c>
-      <c r="O15" s="6">
-        <v>46187</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T15" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z15" s="7">
-        <v>7892.85</v>
-      </c>
-      <c r="AA15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>46101</v>
-      </c>
-      <c r="AD15" s="7">
-        <v>7892.85</v>
-      </c>
-      <c r="AE15" s="4">
-        <v>145</v>
-      </c>
-      <c r="AF15" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="AH15" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="AI15" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="AJ15" s="4"/>
-      <c r="AK15" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL15" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AM15" s="6">
-        <v>46100</v>
-      </c>
-      <c r="AN15" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO15" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C16" s="3">
-        <v>46163</v>
-      </c>
-      <c r="D16" s="4">
-        <v>553378154</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46101</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="K16" s="3">
-        <v>46268</v>
-      </c>
-      <c r="L16" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-61</v>
-      </c>
-      <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>61</v>
-      </c>
-      <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>61</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46221</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z16" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AA16" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>46163</v>
-      </c>
-      <c r="AD16" s="7">
-        <v>7623.07</v>
-      </c>
-      <c r="AE16" s="4">
-        <v>141</v>
-      </c>
-      <c r="AF16" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG16" s="5"/>
-      <c r="AH16" s="5"/>
-      <c r="AI16" s="5"/>
-      <c r="AJ16" s="4"/>
-      <c r="AK16" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL16" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AM16" s="6">
-        <v>46105</v>
-      </c>
-      <c r="AN16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO16" s="5" t="s">
         <v>350</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO16" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <conditionalFormatting sqref="L2:L16">
+  <autoFilter ref="A1:AO14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:L14">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -11725,7 +11155,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M16">
+  <conditionalFormatting sqref="M2:M14">
     <cfRule type="expression" dxfId="34" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -11742,7 +11172,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N16">
+  <conditionalFormatting sqref="N2:N14">
     <cfRule type="expression" dxfId="29" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -11759,7 +11189,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U16">
+  <conditionalFormatting sqref="O2:U14">
     <cfRule type="expression" dxfId="24" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -11777,7 +11207,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A16" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A14" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11788,7 +11218,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO15"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11956,70 +11386,70 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="C2" s="3">
         <v>46113</v>
       </c>
       <c r="D2" s="4">
-        <v>567164585</v>
+        <v>571606148</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F2" s="6">
-        <v>46098</v>
+        <v>46091</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>352</v>
+        <v>67</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>352</v>
+        <v>67</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K2" s="3">
-        <v>46252</v>
+        <v>46278</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L15" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
-        <v>-4</v>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
+        <v>174</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($F2="","",$F2+365-TODAY())</f>
-        <v>181</v>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v>196</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($F2="","",$F2+365-TODAY())</f>
-        <v>181</v>
+        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <v>-49</v>
       </c>
       <c r="O2" s="6">
-        <v>46278</v>
+        <v>46456</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>354</v>
+        <v>69</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>59</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -12028,7 +11458,7 @@
         <v>49</v>
       </c>
       <c r="Z2" s="7">
-        <v>2528.2600000000002</v>
+        <v>1294.23</v>
       </c>
       <c r="AA2" s="7">
         <v>0</v>
@@ -12040,18 +11470,20 @@
         <v>46113</v>
       </c>
       <c r="AD2" s="7">
-        <v>2528.2600000000002</v>
+        <v>1294.23</v>
       </c>
       <c r="AE2" s="4">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AF2" s="5" t="s">
-        <v>149</v>
+        <v>360</v>
       </c>
       <c r="AG2" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="AH2" s="5"/>
+        <v>361</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="4"/>
       <c r="AK2" s="5" t="s">
@@ -12067,7 +11499,7 @@
         <v>356</v>
       </c>
       <c r="AO2" s="5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
@@ -12078,16 +11510,16 @@
         <v>474</v>
       </c>
       <c r="C3" s="3">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="D3" s="4">
-        <v>571606148</v>
+        <v>571606263</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F3" s="6">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>67</v>
@@ -12096,28 +11528,28 @@
         <v>67</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K3" s="3">
         <v>46278</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>174</v>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
+        <v>195</v>
       </c>
       <c r="M3" s="12">
         <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="N3" s="12">
         <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
-        <v>-49</v>
+        <v>-36</v>
       </c>
       <c r="O3" s="6">
-        <v>46456</v>
+        <v>46477</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>59</v>
@@ -12144,7 +11576,7 @@
         <v>49</v>
       </c>
       <c r="Z3" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AA3" s="7">
         <v>0</v>
@@ -12153,22 +11585,22 @@
         <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="AD3" s="7">
-        <v>1294.23</v>
+        <v>2173.29</v>
       </c>
       <c r="AE3" s="4">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AG3" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH3" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="AH3" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="4"/>
@@ -12179,42 +11611,42 @@
         <v>62</v>
       </c>
       <c r="AM3" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN3" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO3" s="5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>474</v>
+      <c r="B4" s="13" t="s">
+        <v>475</v>
       </c>
       <c r="C4" s="3">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="D4" s="4">
-        <v>571606263</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>363</v>
+        <v>571606836</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>375</v>
       </c>
       <c r="F4" s="6">
-        <v>46112</v>
+        <v>46084</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>67</v>
+        <v>376</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>67</v>
+        <v>376</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>364</v>
@@ -12223,34 +11655,34 @@
         <v>46278</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>195</v>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
+        <v>-108</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
-        <v>209</v>
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-108</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
-        <v>-36</v>
+        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
+        <v>11</v>
       </c>
       <c r="O4" s="6">
-        <v>46477</v>
+        <v>46174</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>69</v>
+        <v>316</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>48</v>
@@ -12271,24 +11703,26 @@
         <v>0</v>
       </c>
       <c r="AC4" s="6">
-        <v>46126</v>
+        <v>46113</v>
       </c>
       <c r="AD4" s="7">
         <v>2173.29</v>
       </c>
       <c r="AE4" s="4">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="5" t="s">
-        <v>365</v>
+        <v>199</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="AH4" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="AI4" s="5"/>
+        <v>378</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>372</v>
+      </c>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="5" t="s">
         <v>94</v>
@@ -12297,42 +11731,42 @@
         <v>62</v>
       </c>
       <c r="AM4" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO4" s="5" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>250</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>477</v>
       </c>
       <c r="C5" s="3">
-        <v>46156</v>
+        <v>46135</v>
       </c>
       <c r="D5" s="4">
-        <v>553770568</v>
+        <v>571607238</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F5" s="6">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>369</v>
+        <v>123</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>369</v>
+        <v>123</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>359</v>
@@ -12341,24 +11775,38 @@
         <v>46278</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-138</v>
-      </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
+        <v>-94</v>
+      </c>
+      <c r="M5" s="12">
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>218</v>
+      </c>
+      <c r="N5" s="12">
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <v>218</v>
+      </c>
       <c r="O5" s="6">
-        <v>46144</v>
+        <v>46188</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
+        <v>113</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
@@ -12375,26 +11823,22 @@
         <v>0</v>
       </c>
       <c r="AC5" s="6">
-        <v>46156</v>
+        <v>46135</v>
       </c>
       <c r="AD5" s="7">
         <v>1294.23</v>
       </c>
       <c r="AE5" s="4">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>199</v>
+        <v>381</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="AH5" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="AI5" s="5" t="s">
-        <v>373</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="5" t="s">
         <v>94</v>
@@ -12403,13 +11847,13 @@
         <v>62</v>
       </c>
       <c r="AM5" s="6">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="AN5" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
@@ -12417,55 +11861,53 @@
         <v>250</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C6" s="3">
-        <v>46113</v>
+        <v>46220</v>
       </c>
       <c r="D6" s="4">
-        <v>571606836</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>375</v>
+        <v>553063753</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>384</v>
       </c>
       <c r="F6" s="6">
-        <v>46084</v>
+        <v>46099</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>376</v>
+        <v>154</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>376</v>
+        <v>154</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="K6" s="3">
-        <v>46278</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-108</v>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
+        <v>-93</v>
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-108</v>
+        <v>-93</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
-        <v>11</v>
+        <f ca="1">IF($C6="","",$C6+60-TODAY())</f>
+        <v>-2</v>
       </c>
       <c r="O6" s="6">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>316</v>
+        <v>156</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>112</v>
@@ -12474,7 +11916,7 @@
         <v>47</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>48</v>
@@ -12486,7 +11928,7 @@
         <v>49</v>
       </c>
       <c r="Z6" s="7">
-        <v>2173.29</v>
+        <v>3822.49</v>
       </c>
       <c r="AA6" s="7">
         <v>0</v>
@@ -12495,106 +11937,106 @@
         <v>0</v>
       </c>
       <c r="AC6" s="6">
-        <v>46113</v>
+        <v>46220</v>
       </c>
       <c r="AD6" s="7">
-        <v>2173.29</v>
+        <v>3822.49</v>
       </c>
       <c r="AE6" s="4">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>199</v>
+        <v>386</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>377</v>
+        <v>213</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="AJ6" s="4"/>
       <c r="AK6" s="5" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AM6" s="6">
-        <v>46106</v>
+        <v>46125</v>
       </c>
       <c r="AN6" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO6" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>250</v>
+      <c r="A7" s="13" t="s">
+        <v>479</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C7" s="3">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="D7" s="4">
-        <v>571607238</v>
+        <v>553857983</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F7" s="6">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>123</v>
+        <v>389</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>123</v>
+        <v>376</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="K7" s="3">
         <v>46278</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-94</v>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
+        <v>-93</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>218</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-93</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>218</v>
+        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <v>12</v>
       </c>
       <c r="O7" s="6">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>113</v>
+        <v>316</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>48</v>
@@ -12606,100 +12048,102 @@
         <v>49</v>
       </c>
       <c r="Z7" s="7">
-        <v>1294.23</v>
+        <v>1649.2</v>
       </c>
       <c r="AA7" s="7">
-        <v>0</v>
+        <v>1420.82</v>
       </c>
       <c r="AB7" s="7">
-        <v>0</v>
+        <v>160.93</v>
       </c>
       <c r="AC7" s="6">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="AD7" s="7">
-        <v>1294.23</v>
+        <v>67.45</v>
       </c>
       <c r="AE7" s="4">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>382</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
-      <c r="AJ7" s="4"/>
+      <c r="AJ7" s="4">
+        <v>571607938</v>
+      </c>
       <c r="AK7" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AL7" s="5" t="s">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="AM7" s="6">
-        <v>46119</v>
+        <v>46106</v>
       </c>
       <c r="AN7" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C8" s="3">
-        <v>46220</v>
+        <v>46127</v>
       </c>
       <c r="D8" s="4">
-        <v>553063753</v>
+        <v>569508762</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F8" s="6">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>154</v>
+        <v>376</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>154</v>
+        <v>376</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="K8" s="3"/>
+        <v>359</v>
+      </c>
+      <c r="K8" s="3">
+        <v>46269</v>
+      </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-93</v>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
+        <v>-87</v>
       </c>
       <c r="M8" s="12">
         <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
-        <v>-93</v>
+        <v>-87</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+60-TODAY())</f>
-        <v>-2</v>
+        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <v>25</v>
       </c>
       <c r="O8" s="6">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>156</v>
+        <v>316</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>112</v>
@@ -12708,7 +12152,7 @@
         <v>47</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>48</v>
@@ -12720,7 +12164,7 @@
         <v>49</v>
       </c>
       <c r="Z8" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AA8" s="7">
         <v>0</v>
@@ -12728,107 +12172,103 @@
       <c r="AB8" s="7">
         <v>0</v>
       </c>
-      <c r="AC8" s="6">
-        <v>46220</v>
-      </c>
+      <c r="AC8" s="6"/>
       <c r="AD8" s="7">
-        <v>3822.49</v>
+        <v>1294.23</v>
       </c>
       <c r="AE8" s="4">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>386</v>
+        <v>191</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>213</v>
+        <v>361</v>
       </c>
       <c r="AH8" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>361</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="AI8" s="5"/>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="5" t="s">
-        <v>248</v>
+        <v>94</v>
       </c>
       <c r="AL8" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="AM8" s="6">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="AN8" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO8" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>479</v>
+      <c r="A9" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C9" s="3">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="D9" s="4">
-        <v>553857983</v>
+        <v>571608266</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="F9" s="6">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>389</v>
+        <v>117</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>389</v>
+        <v>43</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="K9" s="3">
         <v>46278</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-93</v>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
+        <v>-87</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
-        <v>-93</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>209</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
-        <v>12</v>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <v>209</v>
       </c>
       <c r="O9" s="6">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>112</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>316</v>
+        <v>118</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>48</v>
@@ -12840,108 +12280,110 @@
         <v>49</v>
       </c>
       <c r="Z9" s="7">
-        <v>1649.2</v>
+        <v>1294.23</v>
       </c>
       <c r="AA9" s="7">
-        <v>1420.82</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="7">
-        <v>160.93</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="6">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="AD9" s="7">
-        <v>67.45</v>
+        <v>1294.23</v>
       </c>
       <c r="AE9" s="4">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="AG9" s="5"/>
-      <c r="AH9" s="5"/>
+        <v>267</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>371</v>
+      </c>
       <c r="AI9" s="5"/>
-      <c r="AJ9" s="4">
-        <v>571607938</v>
-      </c>
+      <c r="AJ9" s="4"/>
       <c r="AK9" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="AM9" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN9" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>476</v>
+        <v>250</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="C10" s="3">
-        <v>46127</v>
-      </c>
-      <c r="D10" s="4">
-        <v>569508762</v>
+        <v>46113</v>
+      </c>
+      <c r="D10" s="14">
+        <v>553787632</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F10" s="6">
-        <v>46105</v>
+        <v>46085</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>359</v>
+      <c r="J10" s="15" t="s">
+        <v>482</v>
       </c>
       <c r="K10" s="3">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-87</v>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-77</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
-        <v>-87</v>
+        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <v>11</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="O10" s="6">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>316</v>
+        <v>349</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>45</v>
@@ -12956,7 +12398,7 @@
         <v>49</v>
       </c>
       <c r="Z10" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AA10" s="7">
         <v>0</v>
@@ -12964,103 +12406,103 @@
       <c r="AB10" s="7">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
+      <c r="AC10" s="6">
+        <v>46113</v>
+      </c>
       <c r="AD10" s="7">
-        <v>1294.23</v>
+        <v>2943.43</v>
       </c>
       <c r="AE10" s="4">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>191</v>
+        <v>391</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="AH10" s="5" t="s">
-        <v>395</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="AM10" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN10" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>250</v>
+        <v>64</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C11" s="3">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="D11" s="4">
-        <v>571608266</v>
+        <v>553810379</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F11" s="6">
-        <v>46105</v>
+        <v>46092</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>117</v>
+        <v>403</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>117</v>
+        <v>403</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="K11" s="3">
+        <v>404</v>
+      </c>
+      <c r="K11" s="16">
         <v>46278</v>
       </c>
       <c r="L11" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-87</v>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
+        <v>-70</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>209</v>
+        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <v>27</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
-        <v>209</v>
+        <f ca="1">IF($C11="","",$C11+180-TODAY())</f>
+        <v>27</v>
       </c>
       <c r="O11" s="6">
-        <v>46195</v>
+        <v>46212</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>48</v>
@@ -13072,7 +12514,7 @@
         <v>49</v>
       </c>
       <c r="Z11" s="7">
-        <v>1294.23</v>
+        <v>879.06</v>
       </c>
       <c r="AA11" s="7">
         <v>0</v>
@@ -13081,59 +12523,57 @@
         <v>0</v>
       </c>
       <c r="AC11" s="6">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="AD11" s="7">
-        <v>1294.23</v>
+        <v>879.06</v>
       </c>
       <c r="AE11" s="4">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>267</v>
+        <v>391</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH11" s="5" t="s">
-        <v>371</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="4"/>
       <c r="AK11" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="AM11" s="6">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="AN11" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>497</v>
+        <v>64</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>483</v>
       </c>
       <c r="C12" s="3">
-        <v>46113</v>
-      </c>
-      <c r="D12" s="14">
-        <v>553787632</v>
+        <v>46127</v>
+      </c>
+      <c r="D12" s="4">
+        <v>555438747</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F12" s="6">
-        <v>46085</v>
+        <v>46112</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>400</v>
@@ -13144,26 +12584,26 @@
       <c r="I12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J12" s="15" t="s">
-        <v>482</v>
-      </c>
-      <c r="K12" s="3">
-        <v>46282</v>
+      <c r="J12" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="K12" s="16">
+        <v>46278</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-77</v>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
+        <v>-50</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" ref="M12:N14" ca="1" si="1">IF($C12="","",$C12+180-TODAY())</f>
-        <v>11</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>25</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <v>25</v>
       </c>
       <c r="O12" s="6">
-        <v>46205</v>
+        <v>46232</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>70</v>
@@ -13190,7 +12630,7 @@
         <v>49</v>
       </c>
       <c r="Z12" s="7">
-        <v>2943.43</v>
+        <v>879.06</v>
       </c>
       <c r="AA12" s="7">
         <v>0</v>
@@ -13199,93 +12639,89 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="AD12" s="7">
-        <v>2943.43</v>
+        <v>879.06</v>
       </c>
       <c r="AE12" s="4">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="AM12" s="6">
-        <v>46106</v>
+        <v>46121</v>
       </c>
       <c r="AN12" s="5" t="s">
         <v>356</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>483</v>
+        <v>250</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="C13" s="3">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="D13" s="4">
-        <v>553810379</v>
+        <v>571612561</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F13" s="6">
-        <v>46092</v>
+        <v>46098</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="K13" s="16">
         <v>46278</v>
       </c>
-      <c r="L13" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-70</v>
+      <c r="L13" s="12" t="str">
+        <f ca="1">IF($O13="","",$O13-TODAY())</f>
+        <v/>
       </c>
       <c r="M13" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <v>44</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="O13" s="6">
-        <v>46212</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>70</v>
-      </c>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>229</v>
+      </c>
+      <c r="O13" s="6"/>
+      <c r="P13" s="5"/>
       <c r="Q13" s="5" t="s">
-        <v>166</v>
+        <v>410</v>
       </c>
       <c r="R13" s="5" t="s">
         <v>45</v>
@@ -13294,7 +12730,7 @@
         <v>48</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>48</v>
@@ -13306,7 +12742,7 @@
         <v>49</v>
       </c>
       <c r="Z13" s="7">
-        <v>879.06</v>
+        <v>3822.49</v>
       </c>
       <c r="AA13" s="7">
         <v>0</v>
@@ -13315,28 +12751,30 @@
         <v>0</v>
       </c>
       <c r="AC13" s="6">
-        <v>46129</v>
+        <v>46146</v>
       </c>
       <c r="AD13" s="7">
-        <v>879.06</v>
+        <v>3822.49</v>
       </c>
       <c r="AE13" s="4">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="AF13" s="5" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="AG13" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="AH13" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>377</v>
+      </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="4"/>
       <c r="AK13" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="AL13" s="5" t="s">
-        <v>392</v>
+        <v>62</v>
       </c>
       <c r="AM13" s="6">
         <v>46106</v>
@@ -13345,242 +12783,12 @@
         <v>356</v>
       </c>
       <c r="AO13" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="C14" s="3">
-        <v>46127</v>
-      </c>
-      <c r="D14" s="4">
-        <v>555438747</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46112</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="K14" s="16">
-        <v>46278</v>
-      </c>
-      <c r="L14" s="12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="M14" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="N14" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="O14" s="6">
-        <v>46232</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z14" s="7">
-        <v>879.06</v>
-      </c>
-      <c r="AA14" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="6">
-        <v>46127</v>
-      </c>
-      <c r="AD14" s="7">
-        <v>879.06</v>
-      </c>
-      <c r="AE14" s="4">
-        <v>130</v>
-      </c>
-      <c r="AF14" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="AG14" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="AH14" s="5"/>
-      <c r="AI14" s="5"/>
-      <c r="AJ14" s="4"/>
-      <c r="AK14" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL14" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM14" s="6">
-        <v>46121</v>
-      </c>
-      <c r="AN14" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO14" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C15" s="3">
-        <v>46146</v>
-      </c>
-      <c r="D15" s="4">
-        <v>571612561</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46098</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="K15" s="16">
-        <v>46278</v>
-      </c>
-      <c r="L15" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
-        <v>44</v>
-      </c>
-      <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
-        <v>229</v>
-      </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="T15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z15" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AA15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>46146</v>
-      </c>
-      <c r="AD15" s="7">
-        <v>3822.49</v>
-      </c>
-      <c r="AE15" s="4">
-        <v>144</v>
-      </c>
-      <c r="AF15" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="AH15" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="AI15" s="5"/>
-      <c r="AJ15" s="4"/>
-      <c r="AK15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AM15" s="6">
-        <v>46106</v>
-      </c>
-      <c r="AN15" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO15" s="5" t="s">
         <v>413</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO15" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <conditionalFormatting sqref="L2:L15">
+  <autoFilter ref="A1:AO13" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:L13">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -13597,7 +12805,7 @@
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M15">
+  <conditionalFormatting sqref="M2:M13">
     <cfRule type="expression" dxfId="14" priority="6">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
@@ -13614,7 +12822,7 @@
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
+  <conditionalFormatting sqref="N2:N13">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
@@ -13631,7 +12839,7 @@
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:U15">
+  <conditionalFormatting sqref="O2:U13">
     <cfRule type="expression" dxfId="4" priority="16">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
@@ -13649,7 +12857,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A15" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A13" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="504">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2572,6 +2572,24 @@
   </si>
   <si>
     <t>Edited dx codes, and resubmitted - DND due to invalid dx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checking tax code on UMR records - I'm expecting a response by email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I need to ask Juan for MR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -5129,10 +5147,10 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C10" s="3">
         <v>46268</v>
@@ -6503,10 +6521,10 @@
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="C22" s="3">
         <v>46124</v>
@@ -7571,7 +7589,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A30" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8959,7 +8977,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9261,10 +9279,10 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C3" s="3">
         <v>46132</v>
@@ -9442,7 +9460,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A3" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11208,7 +11226,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A14" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11858,10 +11876,10 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="C6" s="3">
         <v>46220</v>
@@ -12858,7 +12876,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A13" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12971,7 +12989,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>430</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="506">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2590,6 +2590,12 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -7589,7 +7595,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A30" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8977,7 +8983,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9460,7 +9466,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A3" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11226,7 +11232,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A14" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11994,7 +12000,7 @@
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>480</v>
@@ -12876,7 +12882,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A13" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12989,7 +12995,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="507">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2596,6 +2596,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 days</t>
   </si>
 </sst>
 </file>
@@ -5416,12 +5419,12 @@
         <v>-107</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>217</v>
+        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
+        <v>-108</v>
       </c>
       <c r="N12" s="12">
         <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O12" s="6">
         <v>46175</v>
@@ -5433,10 +5436,10 @@
         <v>113</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>59</v>
@@ -6104,12 +6107,12 @@
         <v>-95</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>218</v>
+        <f ca="1">IF($F18="","",$F18+90-TODAY())</f>
+        <v>-96</v>
       </c>
       <c r="N18" s="12">
         <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O18" s="6">
         <v>46187</v>
@@ -6121,10 +6124,10 @@
         <v>113</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>59</v>
@@ -6564,12 +6567,12 @@
         <v>-91</v>
       </c>
       <c r="M22" s="12">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>207</v>
+        <f ca="1">IF($F22="","",$F22+90-TODAY())</f>
+        <v>-92</v>
       </c>
       <c r="N22" s="12">
         <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O22" s="6">
         <v>46191</v>
@@ -6581,10 +6584,10 @@
         <v>113</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>59</v>
@@ -6795,11 +6798,11 @@
       </c>
       <c r="M24" s="12">
         <f ca="1">IF($F24="","",$F24+90-TODAY())</f>
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="N24" s="12">
-        <f ca="1">IF($C24="","",$C24+60-TODAY())</f>
-        <v>-99</v>
+        <f ca="1">IF($C24="","",$C24+540-TODAY())</f>
+        <v>380</v>
       </c>
       <c r="O24" s="6">
         <v>46196</v>
@@ -6817,7 +6820,7 @@
         <v>47</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>157</v>
+        <v>506</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>48</v>
@@ -10508,11 +10511,11 @@
       </c>
       <c r="M9" s="12">
         <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+60-TODAY())</f>
-        <v>-125</v>
+        <f ca="1">IF($C9="","",$C9+540-TODAY())</f>
+        <v>354</v>
       </c>
       <c r="O9" s="6">
         <v>46177</v>
@@ -10530,7 +10533,7 @@
         <v>47</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>157</v>
+        <v>506</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>48</v>
@@ -10619,12 +10622,12 @@
         <v>-105</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F10="","",$F10+90-TODAY())</f>
+        <v>-106</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O10" s="6">
         <v>46177</v>
@@ -10636,10 +10639,10 @@
         <v>113</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>59</v>
@@ -10736,11 +10739,11 @@
       </c>
       <c r="M11" s="12">
         <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
-        <v>-99</v>
+        <v>-100</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+60-TODAY())</f>
-        <v>-114</v>
+        <f ca="1">IF($C11="","",$C11+540-TODAY())</f>
+        <v>365</v>
       </c>
       <c r="O11" s="6">
         <v>46183</v>
@@ -10758,7 +10761,7 @@
         <v>47</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>157</v>
+        <v>506</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>48</v>
@@ -10854,11 +10857,11 @@
       </c>
       <c r="M12" s="12">
         <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
-        <v>-99</v>
+        <v>-100</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+60-TODAY())</f>
-        <v>-2</v>
+        <f ca="1">IF($C12="","",$C12+540-TODAY())</f>
+        <v>477</v>
       </c>
       <c r="O12" s="6">
         <v>46183</v>
@@ -10876,7 +10879,7 @@
         <v>47</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>157</v>
+        <v>506</v>
       </c>
       <c r="U12" s="5" t="s">
         <v>48</v>
@@ -11803,12 +11806,12 @@
         <v>-94</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>218</v>
+        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <v>32</v>
       </c>
       <c r="N5" s="12">
         <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O5" s="6">
         <v>46188</v>
@@ -11817,10 +11820,10 @@
         <v>112</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S5" s="5" t="s">
         <v>48</v>
@@ -11918,11 +11921,11 @@
       </c>
       <c r="M6" s="12">
         <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-93</v>
+        <v>-94</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+60-TODAY())</f>
-        <v>-2</v>
+        <f ca="1">IF($C6="","",$C6+540-TODAY())</f>
+        <v>477</v>
       </c>
       <c r="O6" s="6">
         <v>46189</v>
@@ -11940,7 +11943,7 @@
         <v>47</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>157</v>
+        <v>506</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>48</v>
@@ -12730,25 +12733,29 @@
       <c r="K13" s="16">
         <v>46278</v>
       </c>
-      <c r="L13" s="12" t="str">
+      <c r="L13" s="12">
         <f ca="1">IF($O13="","",$O13-TODAY())</f>
-        <v/>
+        <v>-95</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
-        <v>44</v>
+        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <v>228</v>
       </c>
       <c r="N13" s="12">
         <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
-        <v>229</v>
-      </c>
-      <c r="O13" s="6"/>
-      <c r="P13" s="5"/>
+        <v>228</v>
+      </c>
+      <c r="O13" s="6">
+        <v>46188</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="Q13" s="5" t="s">
         <v>410</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S13" s="5" t="s">
         <v>48</v>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -235,20 +235,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -438,20 +424,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -647,20 +619,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -853,20 +811,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1056,20 +1000,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -4070,7 +4000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO30"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4108,10 +4038,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -4232,11 +4161,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>64</v>
       </c>
@@ -4346,11 +4272,8 @@
       <c r="AN2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>250</v>
       </c>
@@ -4460,11 +4383,8 @@
       <c r="AN3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>63</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>64</v>
       </c>
@@ -4576,11 +4496,8 @@
       <c r="AN4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>73</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>64</v>
       </c>
@@ -4692,11 +4609,8 @@
       <c r="AN5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>84</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>130</v>
       </c>
@@ -4802,11 +4716,8 @@
       <c r="AN6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>90</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>64</v>
       </c>
@@ -4918,11 +4829,8 @@
       <c r="AN7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>95</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
@@ -5034,11 +4942,8 @@
       <c r="AN8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>99</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>459</v>
       </c>
@@ -5150,11 +5055,8 @@
       <c r="AN9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>104</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>498</v>
       </c>
@@ -5262,11 +5164,8 @@
       <c r="AN10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>106</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>250</v>
       </c>
@@ -5376,11 +5275,8 @@
       <c r="AN11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>250</v>
       </c>
@@ -5490,11 +5386,8 @@
       <c r="AN12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>115</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>250</v>
       </c>
@@ -5604,11 +5497,8 @@
       <c r="AN13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>119</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>459</v>
       </c>
@@ -5720,11 +5610,8 @@
       <c r="AN14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>125</v>
-      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>250</v>
       </c>
@@ -5834,11 +5721,8 @@
       <c r="AN15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO15" s="5" t="s">
-        <v>127</v>
-      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>250</v>
       </c>
@@ -5948,11 +5832,8 @@
       <c r="AN16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO16" s="5" t="s">
-        <v>129</v>
-      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>130</v>
       </c>
@@ -6064,11 +5945,8 @@
       <c r="AN17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO17" s="5" t="s">
-        <v>135</v>
-      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>250</v>
       </c>
@@ -6180,11 +6058,8 @@
       <c r="AN18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO18" s="5" t="s">
-        <v>137</v>
-      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>250</v>
       </c>
@@ -6294,11 +6169,8 @@
       <c r="AN19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO19" s="5" t="s">
-        <v>139</v>
-      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>250</v>
       </c>
@@ -6410,11 +6282,8 @@
       <c r="AN20" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO20" s="5" t="s">
-        <v>142</v>
-      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>446</v>
       </c>
@@ -6524,11 +6393,8 @@
       <c r="AN21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO21" s="5" t="s">
-        <v>144</v>
-      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>498</v>
       </c>
@@ -6638,11 +6504,8 @@
       <c r="AN22" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO22" s="5" t="s">
-        <v>147</v>
-      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
@@ -6754,11 +6617,8 @@
       <c r="AN23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO23" s="5" t="s">
-        <v>152</v>
-      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>64</v>
       </c>
@@ -6870,11 +6730,8 @@
       <c r="AN24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO24" s="5" t="s">
-        <v>158</v>
-      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>250</v>
       </c>
@@ -6984,11 +6841,8 @@
       <c r="AN25" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO25" s="5" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>250</v>
       </c>
@@ -7100,11 +6954,8 @@
       <c r="AN26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO26" s="5" t="s">
-        <v>163</v>
-      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>130</v>
       </c>
@@ -7214,11 +7065,8 @@
       <c r="AN27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO27" s="5" t="s">
-        <v>167</v>
-      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>250</v>
       </c>
@@ -7328,11 +7176,8 @@
       <c r="AN28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO28" s="5" t="s">
-        <v>172</v>
-      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>250</v>
       </c>
@@ -7424,11 +7269,8 @@
       <c r="AN29" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO29" s="5" t="s">
-        <v>176</v>
-      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>446</v>
       </c>
@@ -7522,12 +7364,9 @@
       <c r="AN30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AO30" s="5" t="s">
-        <v>182</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN30" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L30">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -7608,7 +7447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7646,10 +7485,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -7770,11 +7608,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3">
@@ -7880,11 +7715,8 @@
       <c r="AN2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>195</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -7992,11 +7824,8 @@
       <c r="AN3" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>202</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>120</v>
       </c>
@@ -8106,11 +7935,8 @@
       <c r="AN4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>211</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3">
@@ -8220,11 +8046,8 @@
       <c r="AN5" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>216</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3">
@@ -8332,11 +8155,8 @@
       <c r="AN6" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>223</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3">
@@ -8444,11 +8264,8 @@
       <c r="AN7" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>226</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3">
@@ -8558,11 +8375,8 @@
       <c r="AN8" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>232</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>64</v>
       </c>
@@ -8674,11 +8488,8 @@
       <c r="AN9" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>237</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -8792,11 +8603,8 @@
       <c r="AN10" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>244</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -8910,12 +8718,9 @@
       <c r="AN11" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>249</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L11">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -8996,7 +8801,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9034,10 +8839,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -9158,11 +8962,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>250</v>
       </c>
@@ -9282,11 +9083,8 @@
       <c r="AN2" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>263</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>498</v>
       </c>
@@ -9393,12 +9191,9 @@
       <c r="AN3" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>278</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO3" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN3" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L3">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -9479,7 +9274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9517,10 +9312,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -9641,11 +9435,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>250</v>
       </c>
@@ -9757,11 +9548,8 @@
       <c r="AN2" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>283</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>250</v>
       </c>
@@ -9877,11 +9665,8 @@
       <c r="AN3" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>291</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>459</v>
       </c>
@@ -9993,11 +9778,8 @@
       <c r="AN4" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>299</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>250</v>
       </c>
@@ -10115,11 +9897,8 @@
       <c r="AN5" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>305</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>459</v>
       </c>
@@ -10231,11 +10010,8 @@
       <c r="AN6" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>308</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>459</v>
       </c>
@@ -10349,11 +10125,8 @@
       <c r="AN7" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>207</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>250</v>
       </c>
@@ -10467,11 +10240,8 @@
       <c r="AN8" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>318</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>250</v>
       </c>
@@ -10581,11 +10351,8 @@
       <c r="AN9" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>321</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>446</v>
       </c>
@@ -10695,11 +10462,8 @@
       <c r="AN10" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>329</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>250</v>
       </c>
@@ -10813,11 +10577,8 @@
       <c r="AN11" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>333</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>250</v>
       </c>
@@ -10929,11 +10690,8 @@
       <c r="AN12" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>337</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>250</v>
       </c>
@@ -11045,11 +10803,8 @@
       <c r="AN13" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>340</v>
-      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>459</v>
       </c>
@@ -11159,12 +10914,9 @@
       <c r="AN14" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="AO14" s="5" t="s">
-        <v>350</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L14">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -11245,7 +10997,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11283,10 +11035,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -11407,11 +11158,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>250</v>
       </c>
@@ -11525,11 +11273,8 @@
       <c r="AN2" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>362</v>
-      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>250</v>
       </c>
@@ -11643,11 +11388,8 @@
       <c r="AN3" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>367</v>
-      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>250</v>
       </c>
@@ -11763,11 +11505,8 @@
       <c r="AN4" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>379</v>
-      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>250</v>
       </c>
@@ -11879,11 +11618,8 @@
       <c r="AN5" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>383</v>
-      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>498</v>
       </c>
@@ -11997,11 +11733,8 @@
       <c r="AN6" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>387</v>
-      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>504</v>
       </c>
@@ -12113,11 +11846,8 @@
       <c r="AN7" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>393</v>
-      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
@@ -12229,11 +11959,8 @@
       <c r="AN8" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>396</v>
-      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>250</v>
       </c>
@@ -12347,11 +12074,8 @@
       <c r="AN9" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>398</v>
-      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>250</v>
       </c>
@@ -12463,11 +12187,8 @@
       <c r="AN10" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>401</v>
-      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -12579,11 +12300,8 @@
       <c r="AN11" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>405</v>
-      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -12695,11 +12413,8 @@
       <c r="AN12" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>407</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>250</v>
       </c>
@@ -12813,12 +12528,9 @@
       <c r="AN13" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="AO13" s="5" t="s">
-        <v>413</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO13" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN13" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L13">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="513">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2529,6 +2529,24 @@
   </si>
   <si>
     <t xml:space="preserve">540 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66 claims with a date of service in 2026-03 March, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5 - No limit on file: 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -12630,7 +12648,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>415</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -12643,12 +12661,12 @@
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>417</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>418</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -12663,7 +12681,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>421</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -12673,7 +12691,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>423</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -12773,7 +12791,7 @@
     </row>
     <row r="34" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>440</v>
+        <v>512</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="30" x14ac:dyDescent="0.25">

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">Filed reconsideration with the 02/27/2026 order notes for BHE prior to SCS trial + March 2026 Monthly Review Summary - PIQ-90338069 - Jess uploaded MR </t>
   </si>
   <si>
-    <t>***Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</t>
+    <t>Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</t>
   </si>
   <si>
     <t>Bundling with Claim ID 26F500108500 Line ID 1 on date of service 03/24/2026 CPT 64640</t>
@@ -2429,7 +2429,7 @@
     <t>Resubmitted to Optum - DND R10: Optum Behavioral Health Responsibility</t>
   </si>
   <si>
-    <t>***Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</t>
+    <t>Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</t>
   </si>
   <si>
     <t>Corrected ordering/referring provider, and resubmitted</t>
@@ -2444,7 +2444,7 @@
     <t>Resubmitted to UHC as primary - DND This care may be covered by another payer per coordination of benefits</t>
   </si>
   <si>
-    <t xml:space="preserve">***I need to ask Juan for MR </t>
+    <t xml:space="preserve">I need to ask Juan for MR </t>
   </si>
   <si>
     <t>No found</t>
@@ -2465,7 +2465,7 @@
     <t>Corrected cpt codes, added code 7, and resubmitted</t>
   </si>
   <si>
-    <t>***Checking tax code on UMR records - I'm expecting a response by email</t>
+    <t>Checking tax code on UMR records - I'm expecting a response by email</t>
   </si>
   <si>
     <t>Corrected auth #, and resubmitted - UTN # required</t>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -2456,7 +2456,7 @@
     <t>Resubmitted to the same payer - Active coverage on DOS - DND Expenses incurred after coverage terminated</t>
   </si>
   <si>
-    <t>93970 x1, 93925 x1</t>
+    <t>93970 x1; 93925 x1</t>
   </si>
   <si>
     <t>Adjusted balance - 93923 bundled with 93925 - DND 93923  Mutually exclusive procedures cannot be done in the same day/setting</t>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -9119,7 +9119,7 @@
         <v>270</v>
       </c>
       <c r="F3" s="6">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>271</v>
